--- a/data/KernelCTFdata_Configs_mini.xlsx
+++ b/data/KernelCTFdata_Configs_mini.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\研究生\科研\wei\linux相关\ISSTA\test2\version4\RQ1\exp1\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE9B640-5456-48B9-B78C-2E9523340F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,15 +13,23 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="128">
   <si>
     <t>CVE</t>
   </si>
@@ -54,6 +56,15 @@
   </si>
   <si>
     <t>CONFIG_NET_SCH_QFQ</t>
+  </si>
+  <si>
+    <t>CVE-2023-32233</t>
+  </si>
+  <si>
+    <t>6.3.1</t>
+  </si>
+  <si>
+    <t>CONFIG_NF_TABLES</t>
   </si>
   <si>
     <t>CVE-2023-3390</t>
@@ -129,9 +140,6 @@
     <t>6.4.16</t>
   </si>
   <si>
-    <t>CONFIG_NF_TABLES</t>
-  </si>
-  <si>
     <t>CVE-2023-4569</t>
   </si>
   <si>
@@ -233,6 +241,9 @@
   </si>
   <si>
     <t>CVE-2024-0193</t>
+  </si>
+  <si>
+    <t>6.6.121</t>
   </si>
   <si>
     <t>CVE-2024-0582</t>
@@ -415,32 +426,19 @@
   </si>
   <si>
     <t>CVE-2025-40364</t>
-  </si>
-  <si>
-    <t>6.6.121</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.6.6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CVE-2023-32233</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CONFIG_NF_TABLES</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.3.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,7 +449,6 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -459,43 +456,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -503,9 +806,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -520,37 +1065,81 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -800,20 +1389,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -824,7 +1413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -835,7 +1424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -846,648 +1435,650 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="8" ht="27" spans="1:3">
       <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="27" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="27" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="27" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="27" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="27" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="27" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" ht="27" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" ht="27" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" ht="27" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" ht="27" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="C23" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" ht="27" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" ht="27" spans="1:3">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" ht="27" spans="1:3">
+      <c r="A27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" ht="27" spans="1:3">
+      <c r="A29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" ht="27" spans="1:3">
+      <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" ht="27" spans="1:3">
+      <c r="A34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" ht="27" spans="1:3">
+      <c r="A35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" ht="27" spans="1:3">
+      <c r="A36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" ht="27" spans="1:3">
+      <c r="A37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" ht="27" spans="1:3">
+      <c r="A38" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" ht="27" spans="1:3">
+      <c r="A39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="41" ht="27" spans="1:3">
+      <c r="A41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" ht="27" spans="1:3">
+      <c r="A42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" ht="40.5" spans="1:3">
+      <c r="A45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" ht="27" spans="1:3">
+      <c r="A47" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" ht="27" spans="1:3">
+      <c r="A51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" ht="27" spans="1:3">
+      <c r="A52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="53" ht="27" spans="1:3">
+      <c r="A53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="56" ht="27" spans="1:3">
+      <c r="A56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" ht="27" spans="1:3">
+      <c r="A57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B57" s="3" t="s">
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C59">
+  <sortState ref="A2:C59">
     <sortCondition ref="A2:A59"/>
   </sortState>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>